--- a/finance/purchase_request/uom.xlsx
+++ b/finance/purchase_request/uom.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="360">
   <si>
     <t>%</t>
   </si>
@@ -1087,6 +1087,18 @@
   </si>
   <si>
     <t>UM</t>
+  </si>
+  <si>
+    <t>packets</t>
+  </si>
+  <si>
+    <t>pkt</t>
+  </si>
+  <si>
+    <t>cartons</t>
+  </si>
+  <si>
+    <t>ctn</t>
   </si>
 </sst>
 </file>
@@ -1894,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B182"/>
+  <dimension ref="A1:B184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3353,6 +3365,22 @@
         <v>353</v>
       </c>
     </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>357</v>
+      </c>
+      <c r="B183" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>359</v>
+      </c>
+      <c r="B184" t="s">
+        <v>358</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
